--- a/Assignment 8/Parameters_copy.xlsx
+++ b/Assignment 8/Parameters_copy.xlsx
@@ -1,29 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minhyounghong/Desktop/spring 2026/AAE 451/Week 6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://purdue0-my.sharepoint.com/personal/hong411_purdue_edu/Documents/AAE 451/Assignment 8/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D59236-55AE-8340-96A5-6AEE4392ADA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54750D4A-8061-4052-8D5C-4156A0EB7BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Deliverables and tasks" sheetId="2" r:id="rId1"/>
     <sheet name="Sizing - Baseline" sheetId="6" r:id="rId2"/>
     <sheet name="Sizing - Blend" sheetId="4" r:id="rId3"/>
-    <sheet name="Blend" sheetId="5" r:id="rId4"/>
-    <sheet name="Sizing -Grinch" sheetId="3" r:id="rId5"/>
-    <sheet name="Grinch" sheetId="7" r:id="rId6"/>
-    <sheet name="Sizing - Sunfish" sheetId="1" r:id="rId7"/>
-    <sheet name="Sizing - Sunfish_final" sheetId="8" r:id="rId8"/>
-    <sheet name="Sunfish" sheetId="12" r:id="rId9"/>
-    <sheet name="Plane Parameters format" sheetId="11" r:id="rId10"/>
-    <sheet name="Airfoil" sheetId="10" r:id="rId11"/>
+    <sheet name="Blend" sheetId="14" r:id="rId4"/>
+    <sheet name="Blend - old" sheetId="5" r:id="rId5"/>
+    <sheet name="Sizing -Grinch" sheetId="3" r:id="rId6"/>
+    <sheet name="Grinch" sheetId="15" r:id="rId7"/>
+    <sheet name="Grinch - old" sheetId="7" r:id="rId8"/>
+    <sheet name="Sizing - Sunfish" sheetId="1" r:id="rId9"/>
+    <sheet name="Sizing - Sunfish_final" sheetId="8" r:id="rId10"/>
+    <sheet name="Sunfish" sheetId="12" r:id="rId11"/>
+    <sheet name="Plane Parameters format" sheetId="11" r:id="rId12"/>
+    <sheet name="Airfoil" sheetId="13" r:id="rId13"/>
+    <sheet name="Airfoil (orig2)" sheetId="16" r:id="rId14"/>
+    <sheet name="Airfoil_orig" sheetId="10" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -260,7 +264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="172">
   <si>
     <t>Deliverables</t>
   </si>
@@ -394,10 +398,25 @@
     <t>Notes regarding specific stabilizers from Raymer, p. 160(pdf 190)</t>
   </si>
   <si>
+    <t>m - CAD model</t>
+  </si>
+  <si>
+    <t>CAD model</t>
+  </si>
+  <si>
+    <t>NACA64A010</t>
+  </si>
+  <si>
+    <t>0 sweep, 55.4 degrees from horizontal</t>
+  </si>
+  <si>
     <t>Horizontal tail volumne coef</t>
   </si>
   <si>
     <t>Pitch moment</t>
+  </si>
+  <si>
+    <t>Vamsi in Group Chat</t>
   </si>
   <si>
     <t>C_M_a_t</t>
@@ -406,73 +425,172 @@
     <t>C_M_Rro</t>
   </si>
   <si>
+    <t>NACA64A210</t>
+  </si>
+  <si>
     <t>x_ac</t>
   </si>
   <si>
-    <t>Weight</t>
+    <t>Taper ratio</t>
+  </si>
+  <si>
+    <t>n_h</t>
+  </si>
+  <si>
+    <t>de_da</t>
+  </si>
+  <si>
+    <t>c_bar</t>
+  </si>
+  <si>
+    <t>c_r</t>
+  </si>
+  <si>
+    <t>c_ht</t>
+  </si>
+  <si>
+    <t>c_vt</t>
+  </si>
+  <si>
+    <t>b_w</t>
+  </si>
+  <si>
+    <t>l_t</t>
+  </si>
+  <si>
+    <t>l_f</t>
+  </si>
+  <si>
+    <t>d_f</t>
+  </si>
+  <si>
+    <t>l_N</t>
+  </si>
+  <si>
+    <t>d_N</t>
+  </si>
+  <si>
+    <t>S_w</t>
+  </si>
+  <si>
+    <t>S_t</t>
+  </si>
+  <si>
+    <t>S_v</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Swp_w</t>
+  </si>
+  <si>
+    <t>Swp_ht</t>
+  </si>
+  <si>
+    <t>Swp_vt</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>AR_vt</t>
+  </si>
+  <si>
+    <t>AR_ht</t>
+  </si>
+  <si>
+    <t>e_t</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>Qf</t>
+  </si>
+  <si>
+    <t>Qw</t>
+  </si>
+  <si>
+    <t>Qht</t>
+  </si>
+  <si>
+    <t>Qvt</t>
+  </si>
+  <si>
+    <t>Qn</t>
   </si>
   <si>
     <t>W</t>
   </si>
   <si>
-    <t>n_h</t>
+    <t>t_c_w</t>
   </si>
   <si>
-    <t>zero aoa Coefficient of lift</t>
+    <t>t_c_ht</t>
   </si>
   <si>
-    <t>de_da</t>
+    <t>t_c_vt</t>
   </si>
   <si>
-    <t>C_L_a_t</t>
+    <t>l_v</t>
   </si>
   <si>
-    <t>C_L_max</t>
+    <t>m</t>
   </si>
   <si>
-    <t>C_L_rot</t>
+    <t>m2</t>
   </si>
   <si>
-    <t>c_d_0</t>
+    <t>r</t>
   </si>
   <si>
-    <t>C_L_t_NU</t>
+    <t>u</t>
   </si>
   <si>
-    <t>alpha stall</t>
+    <t>kg</t>
   </si>
   <si>
-    <t>AR</t>
+    <t>Fuselage</t>
+  </si>
+  <si>
+    <t>Nacelles</t>
+  </si>
+  <si>
+    <t>These four are in radians!</t>
+  </si>
+  <si>
+    <t>These all are the interferance factors, ref earlier slides</t>
+  </si>
+  <si>
+    <t>It's better if you remove this when copying &amp; pasting for different config, but it won't matter either way</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Values that should be entered in 3rd row</t>
+  </si>
+  <si>
+    <t>m^2</t>
+  </si>
+  <si>
+    <t>radians</t>
+  </si>
+  <si>
+    <t>1/radians</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>unitless</t>
   </si>
   <si>
     <t>Swp</t>
   </si>
   <si>
-    <t>c_bar</t>
-  </si>
-  <si>
-    <t>b_w</t>
-  </si>
-  <si>
-    <t>S_w</t>
-  </si>
-  <si>
-    <t>l_t</t>
-  </si>
-  <si>
-    <t>S_t</t>
-  </si>
-  <si>
     <t>AR_t</t>
-  </si>
-  <si>
-    <t>e_t</t>
-  </si>
-  <si>
-    <t>l_v</t>
-  </si>
-  <si>
-    <t>S_v</t>
   </si>
   <si>
     <t>C_L_0</t>
@@ -496,7 +614,70 @@
     <t>a_s</t>
   </si>
   <si>
+    <t>C_L_a_t</t>
+  </si>
+  <si>
     <t>C_d_0</t>
+  </si>
+  <si>
+    <t>C_L_max</t>
+  </si>
+  <si>
+    <t>C_L_rot</t>
+  </si>
+  <si>
+    <t>C_L_t_NU</t>
+  </si>
+  <si>
+    <t>ft^2 from CAD</t>
+  </si>
+  <si>
+    <t>ft^2 - CAD</t>
+  </si>
+  <si>
+    <t>ft from CAD</t>
+  </si>
+  <si>
+    <t>ft - CAD</t>
+  </si>
+  <si>
+    <t>ft From CAD</t>
+  </si>
+  <si>
+    <t>ft CAD</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VH coeff</t>
+  </si>
+  <si>
+    <t>(St*lt)/(Sw*c)</t>
+  </si>
+  <si>
+    <t>VT coeff</t>
+  </si>
+  <si>
+    <t>(Sv*lv)/(Sw*bw)</t>
+  </si>
+  <si>
+    <t>ft^2 from slides</t>
+  </si>
+  <si>
+    <t>from slides</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>zero aoa Coefficient of lift</t>
+  </si>
+  <si>
+    <t>c_d_0</t>
+  </si>
+  <si>
+    <t>alpha stall</t>
   </si>
   <si>
     <t xml:space="preserve">please let me know if you have successfully migrated all the values into </t>
@@ -541,136 +722,13 @@
     <t>Cld</t>
   </si>
   <si>
-    <t>Swp_w</t>
-  </si>
-  <si>
-    <t>Swp_ht</t>
-  </si>
-  <si>
-    <t>c_ht</t>
-  </si>
-  <si>
-    <t>c_vt</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>c_r</t>
-  </si>
-  <si>
-    <t>l_f</t>
-  </si>
-  <si>
-    <t>d_f</t>
-  </si>
-  <si>
-    <t>l_N</t>
-  </si>
-  <si>
-    <t>d_N</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Swp_vt</t>
-  </si>
-  <si>
-    <t>AR_vt</t>
-  </si>
-  <si>
-    <t>AR_ht</t>
-  </si>
-  <si>
-    <t>Qf</t>
-  </si>
-  <si>
-    <t>Qw</t>
-  </si>
-  <si>
-    <t>Qht</t>
-  </si>
-  <si>
-    <t>Qvt</t>
-  </si>
-  <si>
-    <t>Qn</t>
-  </si>
-  <si>
-    <t>t_c_w</t>
-  </si>
-  <si>
-    <t>t_c_ht</t>
-  </si>
-  <si>
-    <t>t_c_vt</t>
-  </si>
-  <si>
-    <t>S_ht</t>
-  </si>
-  <si>
-    <t>S_vt</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>m2</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
     <t>no nacelles no fuselage</t>
-  </si>
-  <si>
-    <t>These four are in radians!</t>
   </si>
   <si>
     <t>idk man, set to 0</t>
   </si>
   <si>
-    <t>These all are the interferance factors, ref earlier slides</t>
-  </si>
-  <si>
     <t>Delta wing assumption?</t>
-  </si>
-  <si>
-    <t>Fuselage</t>
-  </si>
-  <si>
-    <t>Nacelles</t>
-  </si>
-  <si>
-    <t>It's better if you remove this when copying &amp; pasting for different config, but it won't matter either way</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>Values that should be entered in 3rd row</t>
-  </si>
-  <si>
-    <t>m^2</t>
-  </si>
-  <si>
-    <t>radians</t>
-  </si>
-  <si>
-    <t>1/radians</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>unitless</t>
   </si>
   <si>
     <t>C_L_0_t</t>
@@ -680,6 +738,39 @@
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>these two should not be 0</t>
+  </si>
+  <si>
+    <t>NACA-TN-2235 (64A010 lift &amp; moment) | https://ntrs.nasa.gov/api/citations/19930082878/downloads/19930082878.pdf | Primary section data, lift curves, Cm, stall</t>
+  </si>
+  <si>
+    <t>High-Subsonic Tests of 64-010 / 64A010 | https://digital.library.unt.edu/ark:/67531/metadc58363/ | Mach 0.3–0.9 lift, drag, moment</t>
+  </si>
+  <si>
+    <t>NACA Report 824 (Summary of Airfoil Data) | https://www.abbottaerospace.com/downloads/naca-report-824-summary-of-airfoil-data/ | High-Re drag and lift summaries</t>
+  </si>
+  <si>
+    <t>NACA 6A-Series Data (Loftin) | https://ntrs.nasa.gov/api/citations/20050092351/downloads/20050092351.pdf | Cambered 6-series performance trends</t>
+  </si>
+  <si>
+    <t>AirfoilTools 64A010 | https://airfoiltools.com/airfoil/details?airfoil=naca64a010-il | Coordinates &amp; geometry reference</t>
+  </si>
+  <si>
+    <t>AirfoilTools 64A210 | https://airfoiltools.com/airfoil/details?airfoil=naca64a210-il | Coordinates &amp; camber reference</t>
+  </si>
+  <si>
+    <t>64A010</t>
+  </si>
+  <si>
+    <t>symmetric</t>
+  </si>
+  <si>
+    <t>64A210</t>
+  </si>
+  <si>
+    <t>cambered</t>
   </si>
   <si>
     <t>E is a nondimensional factor relating to the mach break</t>
@@ -695,7 +786,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -784,6 +875,7 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -797,8 +889,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -823,6 +925,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -836,7 +944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -850,6 +958,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3520,7 +3631,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18">
+        <xdr:cNvPr id="19" name="">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35860A9A-5808-A246-5B98-B6256FE82E18}"/>
@@ -6053,504 +6164,6 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>191061</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="224484" cy="185051"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="19" name="TextBox 18">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B853973C-2BEB-924F-BCF2-E37B6B920F40}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2501900" y="5525061"/>
-              <a:ext cx="224484" cy="185051"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐶</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝐿</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>0</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="19" name="TextBox 18">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B853973C-2BEB-924F-BCF2-E37B6B920F40}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2501900" y="5525061"/>
-              <a:ext cx="224484" cy="185051"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐶_(𝐿_0 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="231282" cy="184987"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="20" name="TextBox 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A4E5AC2-41C4-474C-873D-E978C2A3643A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2501900" y="5715000"/>
-              <a:ext cx="231282" cy="184987"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐶</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝐿</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑎</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="20" name="TextBox 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A4E5AC2-41C4-474C-873D-E978C2A3643A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2501900" y="5715000"/>
-              <a:ext cx="231282" cy="184987"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐶_(𝐿_𝑎 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="231795" cy="185500"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="21" name="TextBox 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1ABB33B-1893-DC4A-8168-64264F89D573}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2501900" y="5905500"/>
-              <a:ext cx="231795" cy="185500"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐶</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝐿</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑑</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="21" name="TextBox 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1ABB33B-1893-DC4A-8168-64264F89D573}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2501900" y="5905500"/>
-              <a:ext cx="231795" cy="185500"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐶_(𝐿_𝑑 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>22</xdr:row>
@@ -7038,1021 +6651,6 @@
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐶_(𝑀_𝑑 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="168251" cy="172227"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="26" name="TextBox 25">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79802BAC-46BA-2C42-9AF1-1C51CA69F581}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6113982"/>
-              <a:ext cx="168251" cy="172227"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑎</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑠</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="26" name="TextBox 25">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79802BAC-46BA-2C42-9AF1-1C51CA69F581}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6113982"/>
-              <a:ext cx="168251" cy="172227"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑎_𝑠</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="274819" cy="206916"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="27" name="TextBox 26">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B6B813C-6714-5947-A438-C269B32B23C1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6113982"/>
-              <a:ext cx="274819" cy="206916"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐶</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝐿</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑎</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑡</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                          </m:sub>
-                        </m:sSub>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="27" name="TextBox 26">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B6B813C-6714-5947-A438-C269B32B23C1}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6113982"/>
-              <a:ext cx="274819" cy="206916"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐶_(𝐿_(𝑎_𝑡 ) )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="370166" cy="184987"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="28" name="TextBox 27">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{437E8ECB-DDA6-E64C-962D-225842167747}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6305044"/>
-              <a:ext cx="370166" cy="184987"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐶</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝐿</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑚𝑎𝑥</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="28" name="TextBox 27">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{437E8ECB-DDA6-E64C-962D-225842167747}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6305044"/>
-              <a:ext cx="370166" cy="184987"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐶_(𝐿_𝑚𝑎𝑥 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="315536" cy="184987"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="29" name="TextBox 28">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB9FF34-1C2E-8A4E-A520-96F201A89148}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6496106"/>
-              <a:ext cx="315536" cy="184987"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐶</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝐿</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟𝑜𝑡</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="29" name="TextBox 28">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB9FF34-1C2E-8A4E-A520-96F201A89148}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6496106"/>
-              <a:ext cx="315536" cy="184987"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐶_(𝐿_𝑟𝑜𝑡 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="233975" cy="185051"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="30" name="TextBox 29">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFD7D02A-735E-6C43-844C-AC3814F38BD9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6687168"/>
-              <a:ext cx="233975" cy="185051"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐶</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑑</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>0</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="30" name="TextBox 29">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFD7D02A-735E-6C43-844C-AC3814F38BD9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6687168"/>
-              <a:ext cx="233975" cy="185051"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐶_(𝑑_0 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="357727" cy="210186"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="31" name="TextBox 30">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AC31FD5-C80E-3A43-9365-BB9C3D257266}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6878230"/>
-              <a:ext cx="357727" cy="210186"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐶</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝐿</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑡</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑁𝑈</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                          </m:sub>
-                        </m:sSub>
-                      </m:sub>
-                    </m:sSub>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="31" name="TextBox 30">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AC31FD5-C80E-3A43-9365-BB9C3D257266}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2506283" y="6878230"/>
-              <a:ext cx="357727" cy="210186"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐶_(𝐿_(𝑡_𝑁𝑈 ) )</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -14000,6 +12598,53 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{457F126A-6D78-4B7D-9CA6-572F53716F1A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{45C74767-FCBA-D944-9915-7825032194A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11963400" y="276225"/>
+          <a:ext cx="2533650" cy="4038600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -25020,9 +23665,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -25060,7 +23705,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -25166,7 +23811,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -25308,7 +23953,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -25317,12 +23962,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33ACBDB4-B2A5-4854-8717-B2043A2FE783}">
   <dimension ref="B2:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="26">
+    <row r="2" spans="2:3" ht="26.1">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -25367,7 +24012,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="26">
+    <row r="11" spans="2:3" ht="26.1">
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
@@ -25378,240 +24023,792 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC9758E-F3C2-4910-8A72-1F9BF3C435F4}">
-  <dimension ref="A1:AS14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137048B1-5520-0D4C-8884-B232019FA023}">
+  <dimension ref="B2:U39"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="18" max="18" width="24.28515625" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:21">
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21">
+      <c r="C3" t="s">
+        <v>145</v>
+      </c>
+      <c r="S3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21">
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <f>D7*(D8+D9)/2</f>
+        <v>12.374368675682753</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <f>I7*(I8+I9)/2</f>
+        <v>12.374368675682753</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>19</v>
+      </c>
+      <c r="T5">
+        <f>T7*T8</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <f>$T$6</f>
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <f>$T$6</f>
+        <v>8</v>
+      </c>
+      <c r="R6" t="s">
+        <v>22</v>
+      </c>
+      <c r="T6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <f>$T$7*COS($T$12)</f>
+        <v>4.9497474702731008</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <f>$T$7*COS($T$12)</f>
+        <v>4.9497474702731008</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21">
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <f>$T$8</f>
+        <v>2.5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <f>$T$8</f>
+        <v>2.5</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21">
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9">
+        <f>$T$8</f>
+        <v>2.5</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <f>$T$8</f>
+        <v>2.5</v>
+      </c>
+      <c r="R9" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="6"/>
+    </row>
+    <row r="10" spans="2:21">
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="R10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S10" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10">
+        <f>T7^2/T5</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21">
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11">
+        <f>D7^2/D5</f>
+        <v>1.9798989881092401</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <f>I7^2/I5</f>
+        <v>1.9798989881092401</v>
+      </c>
+      <c r="R11" t="s">
+        <v>31</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21">
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="R12" t="s">
+        <v>146</v>
+      </c>
+      <c r="T12">
+        <v>0.78539816299999998</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21">
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21">
+      <c r="D16">
+        <f>(D5*D6)/(D23*D24)</f>
+        <v>5.0671797001708048E-3</v>
+      </c>
+      <c r="L16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="8">
+        <v>4.7468000000000003E-2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17">
+        <f>(I5*I6)/(D24*D25)</f>
+        <v>1.5239222026882683E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23">
+        <f>Sunfish!B2*0.5*3.28084</f>
+        <v>18.044619999999998</v>
+      </c>
+      <c r="G23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <f>0.5*D25*3.28084*Sunfish!B2</f>
+        <v>1082.6772000000001</v>
+      </c>
+      <c r="G24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25">
+        <v>60</v>
+      </c>
+      <c r="G25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <f>D25^2/D24</f>
+        <v>3.3250908026880031</v>
+      </c>
+      <c r="G26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="G28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="L38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16047538-E6F6-43B6-8921-8FD1869BB084}">
+  <dimension ref="A1:AS7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:45">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H1" t="s">
-        <v>100</v>
-      </c>
       <c r="I1" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="J1" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="K1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M1" t="s">
         <v>70</v>
       </c>
       <c r="N1" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="O1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="Q1" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="R1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="S1" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="T1" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="U1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="V1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="W1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="X1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>111</v>
+        <v>79</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="AD1" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AE1" s="12" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="AF1" s="12" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="AG1" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AH1" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI1" s="12" t="s">
-        <v>116</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI1" s="12"/>
     </row>
     <row r="2" spans="1:45">
+      <c r="A2">
+        <f>'Sizing - Sunfish_final'!D23 * 0.3048</f>
+        <v>5.5000001759999995</v>
+      </c>
+      <c r="B2">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <f>('Sizing - Sunfish_final'!D8 + 'Sizing - Sunfish_final'!D9)* 0.3048 / 2</f>
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="D2">
+        <f>('Sizing - Sunfish_final'!I8 + 'Sizing - Sunfish_final'!I9)* 0.3048 / 2</f>
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="E2">
+        <f>'Sizing - Sunfish_final'!D25 * 0.3048</f>
+        <v>18.288</v>
+      </c>
+      <c r="F2">
+        <f>'Sizing - Sunfish_final'!D6</f>
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>'Sizing - Sunfish_final'!D24 * 0.09290304</f>
+        <v>100.58400321868801</v>
+      </c>
+      <c r="L2">
+        <f>'Sizing - Sunfish_final'!D5</f>
+        <v>12.374368675682753</v>
+      </c>
+      <c r="M2">
+        <f>'Sizing - Sunfish_final'!I5</f>
+        <v>12.374368675682753</v>
+      </c>
+      <c r="N2">
+        <f>'Sizing - Sunfish_final'!D24 * 0.09290304</f>
+        <v>100.58400321868801</v>
+      </c>
+      <c r="O2">
+        <f>('Sizing - Sunfish_final'!D27) * PI() / 180</f>
+        <v>0.58992128717408332</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>'Sizing - Sunfish_final'!D26</f>
+        <v>3.3250908026880031</v>
+      </c>
+      <c r="S2">
+        <f>'Sizing - Sunfish_final'!I11</f>
+        <v>1.9798989881092401</v>
+      </c>
+      <c r="T2">
+        <f>'Sizing - Sunfish_final'!D11</f>
+        <v>1.9798989881092401</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f>B2*0.25</f>
+        <v>2.75</v>
+      </c>
+      <c r="W2">
+        <v>0.9</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1.03</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <f xml:space="preserve"> 53870 * 0.45359237</f>
+        <v>24435.020971900001</v>
+      </c>
       <c r="AE2" s="11">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AF2" s="11">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AG2" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="11">
-        <v>0</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="AH2">
+        <f>F2</f>
+        <v>8</v>
+      </c>
+      <c r="AI2" s="11"/>
     </row>
     <row r="3" spans="1:45">
       <c r="A3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="AE3" s="12" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AF3" s="12" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AG3" s="12" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI3" s="11" t="s">
-        <v>118</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AI3" s="11"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -25625,79 +24822,26 @@
     </row>
     <row r="5" spans="1:45">
       <c r="G5" t="s">
-        <v>127</v>
-      </c>
-      <c r="I5" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="O5" t="s">
-        <v>123</v>
+        <v>97</v>
+      </c>
+      <c r="U5" t="s">
+        <v>153</v>
+      </c>
+      <c r="W5" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:45">
       <c r="Y6" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:45">
-      <c r="A7" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:45">
-      <c r="A8" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:45">
-      <c r="A9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:45">
-      <c r="A10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:45">
-      <c r="A11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:45">
-      <c r="A12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:45">
-      <c r="A13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:45">
-      <c r="A14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" t="s">
-        <v>121</v>
+      <c r="V7" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -25705,2391 +24849,115 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2F6581F-2974-4EDC-B112-90F765F2515F}">
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="C4" s="9"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="C6" s="9"/>
-      <c r="H6" t="s">
-        <v>140</v>
-      </c>
-      <c r="O6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="F7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9AC1EA4-6118-493F-90F3-D34ADE0DF126}">
-  <dimension ref="B2:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12">
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>120</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5">
-        <v>155</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13">
-        <f>(D5*D6)/(D31*D32)</f>
-        <v>0.41739130434782606</v>
-      </c>
-      <c r="G13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="L16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17">
-        <f>(I5*I6)/(D32*D33)</f>
-        <v>0.1040268456375839</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12">
-      <c r="B33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33">
-        <v>44.7</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
-      <c r="B34" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12">
-      <c r="B35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12">
-      <c r="B40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12">
-      <c r="B42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12">
-      <c r="L45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C49C640-B0B2-2C45-B158-C8004F9CBE4B}">
-  <dimension ref="B2:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12">
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="e">
-        <f>D8*D25*D24/D6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="e">
-        <f>AVERAGE(I8:I9)*D23*D24/I6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="G13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="L16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" t="s">
-        <v>29</v>
-      </c>
-      <c r="G26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="G28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" t="s">
-        <v>50</v>
-      </c>
-      <c r="G29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12">
-      <c r="B33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
-      <c r="B34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12">
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12">
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12">
-      <c r="B37" t="s">
-        <v>58</v>
-      </c>
-      <c r="L37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12">
-      <c r="B39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C74934F-44AB-4346-A940-767187D33107}">
-  <dimension ref="A1:AC2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:29">
-      <c r="A1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>75</v>
-      </c>
-      <c r="R1" t="s">
-        <v>76</v>
-      </c>
-      <c r="S1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U1" t="s">
-        <v>46</v>
-      </c>
-      <c r="V1" t="s">
-        <v>78</v>
-      </c>
-      <c r="W1" t="s">
-        <v>48</v>
-      </c>
-      <c r="X1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29">
-      <c r="A2">
-        <f>'Sizing - Blend'!D29</f>
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <f>'Sizing - Blend'!D26</f>
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <f>'Sizing - Blend'!D27</f>
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>'Sizing - Blend'!D23</f>
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <f>'Sizing - Blend'!D25</f>
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <f>'Sizing - Blend'!D24</f>
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <f>'Sizing - Blend'!D6</f>
-        <v>0</v>
-      </c>
-      <c r="H2" t="e">
-        <f>'Sizing - Blend'!D5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I2">
-        <f>'Sizing - Blend'!D10</f>
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <f>'Sizing - Blend'!D12</f>
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <f>'Sizing - Blend'!I6</f>
-        <v>0</v>
-      </c>
-      <c r="L2" t="e">
-        <f>'Sizing - Blend'!I5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M2">
-        <f>'Sizing - Blend'!D30</f>
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <f>'Sizing - Blend'!D31</f>
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <f>'Sizing - Blend'!D32</f>
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <f>'Sizing - Blend'!I23</f>
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <f>'Sizing - Blend'!I24</f>
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <f>'Sizing - Blend'!I25</f>
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <f>'Sizing - Blend'!D39</f>
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <f>'Sizing - Blend'!D33</f>
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <f>'Sizing - Blend'!I26</f>
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <f>'Sizing - Blend'!D36</f>
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <f>'Sizing - Blend'!I28</f>
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <f>'Sizing - Blend'!I29</f>
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <f>'Sizing - Blend'!I30</f>
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <f>'Sizing - Blend'!D34</f>
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <f>'Sizing - Blend'!D35</f>
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <f>'Sizing - Blend'!D37</f>
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <f>'Sizing - Blend'!I27</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671C506B-F31E-9447-ACC5-ABE21B35E24D}">
-  <dimension ref="B2:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12">
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="e">
-        <f>D8*D25*D24/D6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="e">
-        <f>AVERAGE(I8:I9)*D23*D24/I6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="G13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="L16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" t="s">
-        <v>29</v>
-      </c>
-      <c r="G26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="G28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" t="s">
-        <v>50</v>
-      </c>
-      <c r="G29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12">
-      <c r="B33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
-      <c r="B34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12">
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12">
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12">
-      <c r="B37" t="s">
-        <v>58</v>
-      </c>
-      <c r="L37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12">
-      <c r="B39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324E0AB6-596F-3148-A442-DC0E65A9BD72}">
-  <dimension ref="A1:AC2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:29">
-      <c r="A1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>75</v>
-      </c>
-      <c r="R1" t="s">
-        <v>76</v>
-      </c>
-      <c r="S1" t="s">
-        <v>77</v>
-      </c>
-      <c r="T1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U1" t="s">
-        <v>46</v>
-      </c>
-      <c r="V1" t="s">
-        <v>78</v>
-      </c>
-      <c r="W1" t="s">
-        <v>48</v>
-      </c>
-      <c r="X1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29">
-      <c r="A2">
-        <f>'Sizing -Grinch'!D29</f>
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <f>'Sizing -Grinch'!D26</f>
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <f>'Sizing -Grinch'!D27</f>
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>'Sizing -Grinch'!D23</f>
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <f>'Sizing -Grinch'!D25</f>
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <f>'Sizing -Grinch'!D24</f>
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <f>'Sizing -Grinch'!D6</f>
-        <v>0</v>
-      </c>
-      <c r="H2" t="e">
-        <f>'Sizing -Grinch'!D5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I2">
-        <f>'Sizing -Grinch'!D10</f>
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <f>'Sizing -Grinch'!D12</f>
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <f>'Sizing -Grinch'!I6</f>
-        <v>0</v>
-      </c>
-      <c r="L2" t="e">
-        <f>'Sizing -Grinch'!I5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M2">
-        <f>'Sizing -Grinch'!D30</f>
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <f>'Sizing -Grinch'!D31</f>
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <f>'Sizing -Grinch'!D32</f>
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <f>'Sizing -Grinch'!I23</f>
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <f>'Sizing -Grinch'!I24</f>
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <f>'Sizing -Grinch'!I25</f>
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <f>'Sizing -Grinch'!D39</f>
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <f>'Sizing -Grinch'!D33</f>
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <f>'Sizing -Grinch'!I26</f>
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <f>'Sizing -Grinch'!D36</f>
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <f>'Sizing -Grinch'!I28</f>
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <f>'Sizing -Grinch'!I29</f>
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <f>'Sizing -Grinch'!I30</f>
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <f>'Sizing -Grinch'!D34</f>
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <f>'Sizing -Grinch'!D35</f>
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <f>'Sizing -Grinch'!D37</f>
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <f>'Sizing -Grinch'!I27</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:12">
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <f>D7*D8</f>
-        <v>42.443296150031991</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5">
-        <f>I7*I8</f>
-        <v>42.443296150031991</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <f>$D$31</f>
-        <v>15.3</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <f>$D$31</f>
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <f xml:space="preserve"> $D$32*COS($D$37 * 3.14/180)</f>
-        <v>8.4886592300063981</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7">
-        <f xml:space="preserve"> $D$32*COS($D$37 * 3.14/180)</f>
-        <v>8.4886592300063981</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <f>$D$33</f>
-        <v>5</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8">
-        <f>$D$33</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10">
-        <f>D7^2/D5</f>
-        <v>1.6977318460012796</v>
-      </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10">
-        <f>I7^2/I5</f>
-        <v>1.6977318460012796</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14">
-        <f>(D5*D6)/(D21*D20)</f>
-        <v>1.4748717363010521E-2</v>
-      </c>
-      <c r="G14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="L16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="G19" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20">
-        <f>D21/D22</f>
-        <v>27.089283333333334</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21">
-        <v>1625.357</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23">
-        <v>2.2149999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
-      <c r="B31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7">
-      <c r="B32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12">
-      <c r="B33" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
-      <c r="B34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="6"/>
-    </row>
-    <row r="35" spans="2:12">
-      <c r="B35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12">
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12">
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37">
-        <v>45</v>
-      </c>
-      <c r="L37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137048B1-5520-0D4C-8884-B232019FA023}">
-  <dimension ref="B2:U39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="18" max="18" width="24.33203125" customWidth="1"/>
-    <col min="19" max="19" width="17.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:21">
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="2:21">
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
-      <c r="S3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="2:21">
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:21">
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <f>D7*(D8+D9)/2</f>
-        <v>42.426406871192853</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5">
-        <f>I7*(I8+I9)/2</f>
-        <v>42.426406871192853</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-      <c r="R5" t="s">
-        <v>19</v>
-      </c>
-      <c r="T5">
-        <f>T7*T8</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="2:21">
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <f>$T$6</f>
-        <v>15.3</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6">
-        <f>$T$6</f>
-        <v>15.3</v>
-      </c>
-      <c r="R6" t="s">
-        <v>22</v>
-      </c>
-      <c r="T6">
-        <f>15.3</f>
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:21">
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <f>$T$7*COS($T$12)</f>
-        <v>8.4852813742385713</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7">
-        <f>$T$7*COS($T$12)</f>
-        <v>8.4852813742385713</v>
-      </c>
-      <c r="R7" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7">
-        <f>12</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="2:21">
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <f>$T$8</f>
-        <v>5</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8">
-        <f>$T$8</f>
-        <v>5</v>
-      </c>
-      <c r="R8" t="s">
-        <v>25</v>
-      </c>
-      <c r="T8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21">
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9">
-        <f>$T$8</f>
-        <v>5</v>
-      </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9">
-        <f>$T$8</f>
-        <v>5</v>
-      </c>
-      <c r="R9" t="s">
-        <v>27</v>
-      </c>
-      <c r="S9" s="6"/>
-    </row>
-    <row r="10" spans="2:21">
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="G10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="R10" t="s">
-        <v>29</v>
-      </c>
-      <c r="S10" t="s">
-        <v>30</v>
-      </c>
-      <c r="T10">
-        <f>T7^2/T5</f>
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="11" spans="2:21">
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11">
-        <f>D7^2/D5</f>
-        <v>1.6970562748477143</v>
-      </c>
-      <c r="G11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11">
-        <f>I7^2/I5</f>
-        <v>1.6970562748477143</v>
-      </c>
-      <c r="R11" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21">
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="R12" t="s">
-        <v>87</v>
-      </c>
-      <c r="T12">
-        <f>PI()/4</f>
-        <v>0.78539816339744828</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21">
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21">
-      <c r="L16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="8">
-        <v>4.7468000000000003E-2</v>
-      </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23">
-        <f>D24/D25</f>
-        <v>27.089283333333334</v>
-      </c>
-      <c r="G23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24">
-        <v>1625.357</v>
-      </c>
-      <c r="G24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25">
-        <v>60</v>
-      </c>
-      <c r="G25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26">
-        <v>2.2149999999999999</v>
-      </c>
-      <c r="G26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="G27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="G28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" t="s">
-        <v>50</v>
-      </c>
-      <c r="G29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12">
-      <c r="B33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
-      <c r="B34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12">
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12">
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12">
-      <c r="B37" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12">
-      <c r="L38" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12">
-      <c r="B39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16047538-E6F6-43B6-8921-8FD1869BB084}">
-  <dimension ref="A1:AS7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC9758E-F3C2-4910-8A72-1F9BF3C435F4}">
+  <dimension ref="A1:AS14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:45">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H1" t="s">
-        <v>100</v>
-      </c>
       <c r="I1" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="J1" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="K1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M1" t="s">
         <v>70</v>
       </c>
       <c r="N1" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="O1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="P1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="Q1" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="R1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="S1" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="T1" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="U1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="V1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="W1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="X1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z1" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA1" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB1" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC1" s="10" t="s">
-        <v>111</v>
+        <v>79</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>84</v>
       </c>
       <c r="AD1" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AE1" s="12" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="AF1" s="12" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="AG1" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AH1" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI1" s="12" t="s">
-        <v>116</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="12"/>
     </row>
     <row r="2" spans="1:45">
-      <c r="A2">
-        <f>'Sizing - Sunfish_final'!D23 * 0.3048</f>
-        <v>8.2568135600000012</v>
-      </c>
-      <c r="B2">
-        <f xml:space="preserve"> 45 * 0.3048</f>
-        <v>13.716000000000001</v>
-      </c>
-      <c r="C2">
-        <f>('Sizing - Sunfish_final'!D8 + 'Sizing - Sunfish_final'!D9)* 0.3048 / 2</f>
-        <v>1.524</v>
-      </c>
-      <c r="D2">
-        <f>('Sizing - Sunfish_final'!I8 + 'Sizing - Sunfish_final'!I9)* 0.3048 / 2</f>
-        <v>1.524</v>
-      </c>
-      <c r="E2">
-        <f>'Sizing - Sunfish_final'!D25 * 0.3048</f>
-        <v>18.288</v>
-      </c>
-      <c r="F2">
-        <f>'Sizing - Sunfish_final'!D6 * 0.3048</f>
-        <v>4.6634400000000005</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <f>'Sizing - Sunfish_final'!D24 * 0.09290304</f>
-        <v>151.00060638528001</v>
-      </c>
-      <c r="L2">
-        <f>'Sizing - Sunfish_final'!D5 * 0.09290304</f>
-        <v>3.9415421746107047</v>
-      </c>
-      <c r="M2">
-        <f>'Sizing - Sunfish_final'!I5 * 0.09290304</f>
-        <v>3.9415421746107047</v>
-      </c>
-      <c r="N2">
-        <f>'Sizing - Sunfish_final'!D24 * 0.09290304</f>
-        <v>151.00060638528001</v>
-      </c>
-      <c r="O2">
-        <f>('Sizing - Sunfish_final'!D27) * PI() / 180</f>
-        <v>0.58992128717408332</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <f>'Sizing - Sunfish_final'!D26</f>
-        <v>2.2149999999999999</v>
-      </c>
-      <c r="S2">
-        <f>'Sizing - Sunfish_final'!I11</f>
-        <v>1.6970562748477143</v>
-      </c>
-      <c r="T2">
-        <f>'Sizing - Sunfish_final'!D11</f>
-        <v>1.6970562748477143</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <f>B2*0.5</f>
-        <v>6.8580000000000005</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
-      <c r="Z2">
-        <v>1</v>
-      </c>
-      <c r="AA2">
-        <v>1.03</v>
-      </c>
-      <c r="AB2">
-        <v>1</v>
-      </c>
-      <c r="AC2">
-        <v>1</v>
-      </c>
-      <c r="AD2">
-        <f xml:space="preserve"> 53870 * 0.45359237</f>
-        <v>24435.020971900001</v>
-      </c>
       <c r="AE2" s="11">
         <v>0</v>
       </c>
@@ -28099,119 +24967,111 @@
       <c r="AG2" s="11">
         <v>0</v>
       </c>
-      <c r="AH2" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="11">
-        <v>0</v>
-      </c>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
     </row>
     <row r="3" spans="1:45">
       <c r="A3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE3" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AF3" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG3" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH3" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI3" s="11" t="s">
-        <v>118</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AE3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -28225,29 +25085,3313 @@
     </row>
     <row r="5" spans="1:45">
       <c r="G5" t="s">
-        <v>122</v>
+        <v>95</v>
+      </c>
+      <c r="I5" t="s">
+        <v>96</v>
       </c>
       <c r="O5" t="s">
-        <v>123</v>
-      </c>
-      <c r="U5" t="s">
-        <v>124</v>
-      </c>
-      <c r="W5" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:45">
       <c r="Y6" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:45">
-      <c r="V7" t="s">
-        <v>126</v>
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45">
+      <c r="A8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:45">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAE273A-F5D4-4B20-99A7-72DA172583BB}">
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="15" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="D2" s="11">
+        <v>1.3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-0.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="I2" s="11">
+        <v>4.5750000000000002</v>
+      </c>
+      <c r="J2" s="11">
+        <v>0</v>
+      </c>
+      <c r="K2" s="11">
+        <v>-0.05</v>
+      </c>
+      <c r="L2" s="15">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11">
+        <v>6</v>
+      </c>
+      <c r="N2" s="15">
+        <v>0</v>
+      </c>
+      <c r="O2" s="11">
+        <v>0.29452400000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="C5" s="9"/>
+      <c r="L5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="C7" s="9"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="C16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2459175D-B360-4AF4-ADC5-C376148FE01B}">
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>0.2</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>-0.05</v>
+      </c>
+      <c r="D2">
+        <v>1.3</v>
+      </c>
+      <c r="E2">
+        <v>1.2</v>
+      </c>
+      <c r="F2">
+        <v>-0.6</v>
+      </c>
+      <c r="G2">
+        <v>-0.05</v>
+      </c>
+      <c r="H2">
+        <v>0.85</v>
+      </c>
+      <c r="I2">
+        <f>6.1</f>
+        <v>6.1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>-0.05</v>
+      </c>
+      <c r="L2" s="10">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="N2" s="10">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>13.5 * PI() / 180</f>
+        <v>0.23561944901923448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="C5" s="9"/>
+      <c r="L5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="C7" s="9"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="C16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2F6581F-2974-4EDC-B112-90F765F2515F}">
+  <dimension ref="A1:R21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E2">
+        <v>1.05</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0.85</v>
+      </c>
+      <c r="I2">
+        <v>6.1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>165</v>
+      </c>
+      <c r="R2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3">
+        <v>0.2</v>
+      </c>
+      <c r="B3">
+        <v>0.18</v>
+      </c>
+      <c r="C3">
+        <v>-0.05</v>
+      </c>
+      <c r="D3">
+        <v>1.3</v>
+      </c>
+      <c r="E3">
+        <v>1.2</v>
+      </c>
+      <c r="F3">
+        <v>0.18</v>
+      </c>
+      <c r="G3">
+        <v>-0.05</v>
+      </c>
+      <c r="H3">
+        <v>0.85</v>
+      </c>
+      <c r="I3">
+        <v>6.1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>-0.05</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>6</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>13.5</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>167</v>
+      </c>
+      <c r="R3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="C5" s="9"/>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="C7" s="9"/>
+      <c r="H7" t="s">
+        <v>169</v>
+      </c>
+      <c r="O7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="F8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="C16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9AC1EA4-6118-493F-90F3-D34ADE0DF126}">
+  <dimension ref="B2:L45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>120</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>155</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13">
+        <f>(D5*D6)/(D31*D32)</f>
+        <v>0.41739130434782606</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="L16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17">
+        <f>(I5*I6)/(D32*D33)</f>
+        <v>0.1040268456375839</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12">
+      <c r="B40" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="L45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C49C640-B0B2-2C45-B158-C8004F9CBE4B}">
+  <dimension ref="B2:L37"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>6.24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>4.6239999999999997</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>6.0810000000000004</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>6.2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>8.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>5.3150000000000004</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>1.905</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>1.905</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>49.4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="L16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="e">
+        <f>(D5*D6)/(D24*D23)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17">
+        <f>(I5*I6)/(D24*D25)</f>
+        <v>0.10390558103678493</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>20.763999999999999</v>
+      </c>
+      <c r="E24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25">
+        <v>13.288</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>3.8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="G29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="G30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="12:12">
+      <c r="L37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02AB0A46-4231-4173-B2B6-9F8E27E5F1D2}">
+  <dimension ref="A1:AQ14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:43">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T1" t="s">
+        <v>77</v>
+      </c>
+      <c r="U1" t="s">
+        <v>78</v>
+      </c>
+      <c r="V1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W1" t="s">
+        <v>56</v>
+      </c>
+      <c r="X1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE1" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF1" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG1" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>2 * Blend!A2*'Sizing - Blend'!D29/('Sizing - Blend'!D29 + 1)</f>
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <f>'Sizing - Blend'!D5/'Sizing - Blend'!D7</f>
+        <v>0.73411764705882354</v>
+      </c>
+      <c r="D2">
+        <f>'Sizing - Blend'!I5/'Sizing - Blend'!I7</f>
+        <v>0.86999059266227641</v>
+      </c>
+      <c r="E2">
+        <f>'Sizing - Blend'!D25</f>
+        <v>13.288</v>
+      </c>
+      <c r="F2">
+        <v>6.2</v>
+      </c>
+      <c r="G2">
+        <v>12</v>
+      </c>
+      <c r="H2">
+        <v>1.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>A2*E2</f>
+        <v>26.576000000000001</v>
+      </c>
+      <c r="L2">
+        <f>'Sizing - Blend'!D5</f>
+        <v>6.24</v>
+      </c>
+      <c r="M2">
+        <f>'Sizing - Blend'!I5</f>
+        <v>4.6239999999999997</v>
+      </c>
+      <c r="N2">
+        <f>K2 + L2 + M2 - B2*H2</f>
+        <v>32.940000000000005</v>
+      </c>
+      <c r="O2">
+        <f>'Sizing - Blend'!D27 * PI() / 180</f>
+        <v>0.62831853071795862</v>
+      </c>
+      <c r="P2">
+        <f>'Sizing - Blend'!D11 * PI() / 180</f>
+        <v>0.86219265048519877</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>E2^2/N2</f>
+        <v>5.3603808136004849</v>
+      </c>
+      <c r="S2">
+        <f>M2/D2^2</f>
+        <v>6.1092614619377175</v>
+      </c>
+      <c r="T2">
+        <f>L2/C2^2</f>
+        <v>11.578525641025641</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f xml:space="preserve"> 0.15 * A2</f>
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.9</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1.04</v>
+      </c>
+      <c r="AB2">
+        <v>1.04</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <f xml:space="preserve"> 83000 * 0.45359237</f>
+        <v>37648.166710000005</v>
+      </c>
+      <c r="AE2" s="11">
+        <v>0.06</v>
+      </c>
+      <c r="AF2" s="11">
+        <v>0.06</v>
+      </c>
+      <c r="AG2" s="11">
+        <v>0.06</v>
+      </c>
+      <c r="AH2">
+        <f>F2</f>
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43">
+      <c r="A3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC3" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI3" s="11"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+      <c r="AM3" s="11"/>
+      <c r="AN3" s="11"/>
+      <c r="AO3" s="11"/>
+      <c r="AP3" s="11"/>
+      <c r="AQ3" s="11"/>
+    </row>
+    <row r="5" spans="1:43">
+      <c r="G5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43">
+      <c r="Y6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43">
+      <c r="A8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C74934F-44AB-4346-A940-767187D33107}">
+  <dimension ref="A1:AC2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:29">
+      <c r="A1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>113</v>
+      </c>
+      <c r="R1" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V1" t="s">
+        <v>117</v>
+      </c>
+      <c r="W1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2">
+        <f>'Sizing - Blend'!D29</f>
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <f>'Sizing - Blend'!D26</f>
+        <v>3.8</v>
+      </c>
+      <c r="C2">
+        <f>'Sizing - Blend'!D27</f>
+        <v>36</v>
+      </c>
+      <c r="D2">
+        <f>'Sizing - Blend'!D23</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>'Sizing - Blend'!D25</f>
+        <v>13.288</v>
+      </c>
+      <c r="F2">
+        <f>'Sizing - Blend'!D24</f>
+        <v>20.763999999999999</v>
+      </c>
+      <c r="G2">
+        <f>'Sizing - Blend'!D6</f>
+        <v>6.0810000000000004</v>
+      </c>
+      <c r="H2">
+        <f>'Sizing - Blend'!D5</f>
+        <v>6.24</v>
+      </c>
+      <c r="I2">
+        <f>'Sizing - Blend'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>'Sizing - Blend'!D12</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>'Sizing - Blend'!I6</f>
+        <v>6.2</v>
+      </c>
+      <c r="L2">
+        <f>'Sizing - Blend'!I5</f>
+        <v>4.6239999999999997</v>
+      </c>
+      <c r="M2">
+        <f>'Sizing - Blend'!D30</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>'Sizing - Blend'!D31</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>'Sizing - Blend'!D32</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>'Sizing - Blend'!I23</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>'Sizing - Blend'!I24</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>'Sizing - Blend'!I25</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>'Sizing - Blend'!D39</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>'Sizing - Blend'!D33</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>'Sizing - Blend'!I26</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f>'Sizing - Blend'!D36</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f>'Sizing - Blend'!I28</f>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f>'Sizing - Blend'!I29</f>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f>'Sizing - Blend'!I30</f>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f>'Sizing - Blend'!D34</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>'Sizing - Blend'!D35</f>
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <f>'Sizing - Blend'!D37</f>
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <f>'Sizing - Blend'!I27</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671C506B-F31E-9447-ACC5-ABE21B35E24D}">
+  <dimension ref="B2:L39"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <f>D8*D7/2</f>
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <f xml:space="preserve"> AVERAGE(I8,I9)*I7/2</f>
+        <v>60.145999999999994</v>
+      </c>
+      <c r="J5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>-10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <f>8.296*2</f>
+        <v>16.591999999999999</v>
+      </c>
+      <c r="J7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>1.2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="J8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>4.79</v>
+      </c>
+      <c r="J9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <f>D7^2/D5</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <f>I7^2/I5</f>
+        <v>4.5771034482758619</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12">
+        <v>30</v>
+      </c>
+      <c r="J12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="L16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17">
+        <f>(D5*D6)/(D24*D23)</f>
+        <v>-1.1829652996845426E-3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" t="s">
+        <v>131</v>
+      </c>
+      <c r="J17">
+        <f>(I5*I6)/(D24*D25)</f>
+        <v>4.312159449383424E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>2536</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25">
+        <v>55</v>
+      </c>
+      <c r="E25" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>3.71</v>
+      </c>
+      <c r="E26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" t="s">
+        <v>120</v>
+      </c>
+      <c r="L37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D2C0D8-F842-4197-A771-3630AF8AE9A9}">
+  <dimension ref="A1:AS14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="20" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:45">
+      <c r="A1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="U1" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="V1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="W1" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="X1" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y1" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z1" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB1" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC1" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD1" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE1" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF1" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG1" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH1" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI1" s="12"/>
+    </row>
+    <row r="2" spans="1:45">
+      <c r="A2" s="13">
+        <f>'Sizing -Grinch'!D23 * 0.3048</f>
+        <v>3.048</v>
+      </c>
+      <c r="B2" s="13">
+        <f>2 *A2 -  (2.59 * 0.3048)</f>
+        <v>5.3065680000000004</v>
+      </c>
+      <c r="C2" s="13">
+        <f>'Sizing -Grinch'!D8 * 0.3048</f>
+        <v>0.36576000000000003</v>
+      </c>
+      <c r="D2" s="13">
+        <f>'Sizing -Grinch'!I8 * 0.3048</f>
+        <v>2.9596080000000002</v>
+      </c>
+      <c r="E2" s="13">
+        <f>'Sizing -Grinch'!D25 * 0.3048</f>
+        <v>16.763999999999999</v>
+      </c>
+      <c r="F2" s="13">
+        <f>'Sizing -Grinch'!D6 * 0.3048</f>
+        <v>-3.048</v>
+      </c>
+      <c r="G2" s="13">
+        <f>42.5 * 0.3048</f>
+        <v>12.954000000000001</v>
+      </c>
+      <c r="H2" s="13">
+        <v>2.051304</v>
+      </c>
+      <c r="I2" s="13">
+        <v>0</v>
+      </c>
+      <c r="J2" s="13">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13">
+        <f xml:space="preserve"> A2*E2 - B2*H2</f>
+        <v>40.211287835327994</v>
+      </c>
+      <c r="L2" s="13">
+        <f xml:space="preserve"> 'Sizing -Grinch'!D5 * 0.09290304</f>
+        <v>0.27870912000000003</v>
+      </c>
+      <c r="M2" s="13">
+        <f xml:space="preserve"> 'Sizing -Grinch'!I5 * 0.09290304</f>
+        <v>5.5877462438399998</v>
+      </c>
+      <c r="N2" s="13">
+        <f xml:space="preserve"> A2*E2</f>
+        <v>51.096671999999998</v>
+      </c>
+      <c r="O2" s="13">
+        <v>0.78539800000000004</v>
+      </c>
+      <c r="P2" s="13">
+        <f>'Sizing -Grinch'!D11 * PI() / 180</f>
+        <v>0.78539816339744828</v>
+      </c>
+      <c r="Q2" s="13">
+        <f>'Sizing -Grinch'!I12 * PI() / 180</f>
+        <v>0.52359877559829882</v>
+      </c>
+      <c r="R2" s="13">
+        <f>E2^2 / K2</f>
+        <v>6.9888757890787323</v>
+      </c>
+      <c r="S2" s="13">
+        <f>'Sizing -Grinch'!I11</f>
+        <v>4.5771034482758619</v>
+      </c>
+      <c r="T2" s="13">
+        <f>'Sizing -Grinch'!D10</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="U2" s="13">
+        <v>0</v>
+      </c>
+      <c r="V2" s="13">
+        <f>0.15*A2</f>
+        <v>0.4572</v>
+      </c>
+      <c r="W2" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="X2" s="13">
+        <v>-0.05</v>
+      </c>
+      <c r="Y2" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="13">
+        <v>1.04</v>
+      </c>
+      <c r="AB2" s="13">
+        <v>1.04</v>
+      </c>
+      <c r="AC2" s="13">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="13">
+        <v>37648.17</v>
+      </c>
+      <c r="AE2" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="AF2" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="AG2" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="AH2" s="13">
+        <v>3.048</v>
+      </c>
+      <c r="AI2" s="11"/>
+    </row>
+    <row r="3" spans="1:45">
+      <c r="A3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="U3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="V3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="X3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD3" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI3" s="11"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+      <c r="AM3" s="11"/>
+      <c r="AN3" s="11"/>
+      <c r="AO3" s="11"/>
+      <c r="AP3" s="11"/>
+      <c r="AQ3" s="11"/>
+      <c r="AR3" s="11"/>
+      <c r="AS3" s="11"/>
+    </row>
+    <row r="5" spans="1:45">
+      <c r="G5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45">
+      <c r="Y6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45">
+      <c r="A7" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45">
+      <c r="A8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:45">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324E0AB6-596F-3148-A442-DC0E65A9BD72}">
+  <dimension ref="A1:AC2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:29">
+      <c r="A1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>113</v>
+      </c>
+      <c r="R1" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V1" t="s">
+        <v>117</v>
+      </c>
+      <c r="W1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2">
+        <f>'Sizing -Grinch'!D29</f>
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f>'Sizing -Grinch'!D26</f>
+        <v>3.71</v>
+      </c>
+      <c r="C2">
+        <f>'Sizing -Grinch'!D27</f>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>'Sizing -Grinch'!D23</f>
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <f>'Sizing -Grinch'!D25</f>
+        <v>55</v>
+      </c>
+      <c r="F2">
+        <f>'Sizing -Grinch'!D24</f>
+        <v>2536</v>
+      </c>
+      <c r="G2">
+        <f>'Sizing -Grinch'!D6</f>
+        <v>-10</v>
+      </c>
+      <c r="H2">
+        <f>'Sizing -Grinch'!D5</f>
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <f>'Sizing -Grinch'!D10</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="J2">
+        <f>'Sizing -Grinch'!D12</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>'Sizing -Grinch'!I6</f>
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <f>'Sizing -Grinch'!I5</f>
+        <v>60.145999999999994</v>
+      </c>
+      <c r="M2">
+        <f>'Sizing -Grinch'!D30</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>'Sizing -Grinch'!D31</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>'Sizing -Grinch'!D32</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>'Sizing -Grinch'!I23</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>'Sizing -Grinch'!I24</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>'Sizing -Grinch'!I25</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>'Sizing -Grinch'!D39</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>'Sizing -Grinch'!D33</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>'Sizing -Grinch'!I26</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f>'Sizing -Grinch'!D36</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f>'Sizing -Grinch'!I28</f>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f>'Sizing -Grinch'!I29</f>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f>'Sizing -Grinch'!I30</f>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f>'Sizing -Grinch'!D34</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>'Sizing -Grinch'!D35</f>
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <f>'Sizing -Grinch'!D37</f>
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <f>'Sizing -Grinch'!I27</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:L37"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <f>D7*D8</f>
+        <v>42.443296150031991</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <f>I7*I8</f>
+        <v>42.443296150031991</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <f>$D$31</f>
+        <v>15.3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6">
+        <f>$D$31</f>
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <f xml:space="preserve"> $D$32*COS($D$37 * 3.14/180)</f>
+        <v>8.4886592300063981</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <f xml:space="preserve"> $D$32*COS($D$37 * 3.14/180)</f>
+        <v>8.4886592300063981</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <f>$D$33</f>
+        <v>5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <f>$D$33</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <f>D7^2/D5</f>
+        <v>1.6977318460012796</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10">
+        <f>I7^2/I5</f>
+        <v>1.6977318460012796</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14">
+        <f>(D5*D6)/(D21*D20)</f>
+        <v>1.4748717363010521E-2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="L16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="G19" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20">
+        <f>D21/D22</f>
+        <v>27.089283333333334</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>1625.357</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23">
+        <v>2.2149999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="6"/>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37">
+        <v>45</v>
+      </c>
+      <c r="L37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>